--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Dausa/excel/Dausa_Survey_Analysis_Master.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Dausa/excel/Dausa_Survey_Analysis_Master.xlsx
@@ -4166,7 +4166,7 @@
         <v>5</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">

--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Dausa/excel/Dausa_Survey_Analysis_Master.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Dausa/excel/Dausa_Survey_Analysis_Master.xlsx
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3880501</v>
+        <v>3862501</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>228264.7647058823</v>
+        <v>275892.9285714286</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1541501</v>
+        <v>1523501</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>258000</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2216500</v>
+        <v>2198500</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>348000</v>
@@ -4163,10 +4163,10 @@
         <v>7</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -4761,7 +4761,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4804,7 +4804,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>0.2075471698113208</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="5">
@@ -4817,7 +4817,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -4830,7 +4830,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -4843,7 +4843,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -4856,7 +4856,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>0.3962264150943396</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="9">
@@ -4908,7 +4908,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>0.2264150943396226</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="14">
@@ -4921,7 +4921,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>0.3207547169811321</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="15">
@@ -4934,7 +4934,7 @@
         <v>12</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.2264150943396226</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="16">
@@ -4973,7 +4973,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="25" t="n">
-        <v>0.169811320754717</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="19">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="C2" s="27" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3"/>
@@ -5063,10 +5063,10 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>0.6981132075471698</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="6">
@@ -5079,7 +5079,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>0.3018867924528302</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="7">
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>0.2264150943396226</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -5194,7 +5194,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D16" s="25" t="n">
-        <v>0.4905660377358491</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="17">
@@ -5220,7 +5220,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>0.2641509433962264</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="18">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="22">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22" s="25" t="n">
-        <v>0.9811320754716981</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.6415094339622641</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="24">
@@ -5310,7 +5310,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="25">
@@ -5323,7 +5323,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="25" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="26">
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D26" s="25" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D27" s="25" t="n">
-        <v>0.5849056603773585</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="28">
@@ -5400,7 +5400,7 @@
         <v>2</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="32">
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" s="25" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="33">
@@ -5426,7 +5426,7 @@
         <v>19</v>
       </c>
       <c r="D33" s="25" t="n">
-        <v>0.3584905660377358</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="34">
@@ -5439,7 +5439,7 @@
         <v>5</v>
       </c>
       <c r="D34" s="25" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="35">
@@ -5452,7 +5452,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="36">
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -5529,7 +5529,7 @@
         <v>3</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="42">
@@ -5606,7 +5606,7 @@
         <v>16</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>0.3018867924528302</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="48">
@@ -5619,7 +5619,7 @@
         <v>3</v>
       </c>
       <c r="D48" s="25" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="49">
@@ -5632,7 +5632,7 @@
         <v>22</v>
       </c>
       <c r="D49" s="25" t="n">
-        <v>0.4150943396226415</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="50">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D50" s="25" t="n">
-        <v>0.1886792452830189</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="51">
@@ -5696,7 +5696,7 @@
         <v>6</v>
       </c>
       <c r="D54" s="25" t="n">
-        <v>0.1132075471698113</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="55">
@@ -5709,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="56">
@@ -5722,7 +5722,7 @@
         <v>13</v>
       </c>
       <c r="D56" s="25" t="n">
-        <v>0.2452830188679245</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="57">
@@ -5735,7 +5735,7 @@
         <v>7</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="58">
@@ -5748,7 +5748,7 @@
         <v>12</v>
       </c>
       <c r="D58" s="25" t="n">
-        <v>0.2264150943396226</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="59">
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>0.169811320754717</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="60">
@@ -5787,7 +5787,7 @@
         <v>3</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="62">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D66" s="25" t="n">
-        <v>0.3773584905660378</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="67">
@@ -5864,7 +5864,7 @@
         <v>25</v>
       </c>
       <c r="D67" s="25" t="n">
-        <v>0.4716981132075472</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68">
@@ -5877,7 +5877,7 @@
         <v>4</v>
       </c>
       <c r="D68" s="25" t="n">
-        <v>0.07547169811320754</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="69">
@@ -5890,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="70">
@@ -5903,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="71">
@@ -5954,7 +5954,7 @@
         <v>2</v>
       </c>
       <c r="D74" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="75">
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>0.5849056603773585</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="76">
@@ -5980,7 +5980,7 @@
         <v>13</v>
       </c>
       <c r="D76" s="25" t="n">
-        <v>0.2452830188679245</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="77">
@@ -5993,7 +5993,7 @@
         <v>4</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>0.07547169811320754</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="78">
@@ -6006,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="D78" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="79">
@@ -6083,7 +6083,7 @@
         <v>4</v>
       </c>
       <c r="D84" s="25" t="n">
-        <v>0.07547169811320754</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="85">
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D85" s="25" t="n">
-        <v>0.169811320754717</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="86">
@@ -6109,7 +6109,7 @@
         <v>3</v>
       </c>
       <c r="D86" s="25" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="87">
@@ -6122,7 +6122,7 @@
         <v>3</v>
       </c>
       <c r="D87" s="25" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="88">
@@ -6135,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="89">
@@ -6148,7 +6148,7 @@
         <v>2</v>
       </c>
       <c r="D89" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="90">
@@ -6161,7 +6161,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="91">
@@ -6174,7 +6174,7 @@
         <v>5</v>
       </c>
       <c r="D91" s="25" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="92">
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D92" s="25" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="93">
@@ -6200,7 +6200,7 @@
         <v>15</v>
       </c>
       <c r="D93" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="94">
@@ -6248,10 +6248,10 @@
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D97" s="25" t="n">
-        <v>0.6981132075471698</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="98">
@@ -6264,7 +6264,7 @@
         <v>24</v>
       </c>
       <c r="D98" s="25" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="99">
@@ -6277,7 +6277,7 @@
         <v>43</v>
       </c>
       <c r="D99" s="25" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="100">
@@ -6316,7 +6316,7 @@
         <v>24</v>
       </c>
       <c r="D102" s="25" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="103">
@@ -6342,7 +6342,7 @@
         <v>39</v>
       </c>
       <c r="D104" s="25" t="n">
-        <v>0.7358490566037735</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="105">
@@ -6355,7 +6355,7 @@
         <v>39</v>
       </c>
       <c r="D105" s="25" t="n">
-        <v>0.7358490566037735</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="106">
@@ -6368,7 +6368,7 @@
         <v>11</v>
       </c>
       <c r="D106" s="25" t="n">
-        <v>0.2075471698113208</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="107">
@@ -6381,7 +6381,7 @@
         <v>5</v>
       </c>
       <c r="D107" s="25" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="108">
@@ -6420,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="111">
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D114" s="25" t="n">
-        <v>0.6792452830188679</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="115">
@@ -6484,7 +6484,7 @@
         <v>12</v>
       </c>
       <c r="D115" s="25" t="n">
-        <v>0.2264150943396226</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="116">
@@ -6497,7 +6497,7 @@
         <v>15</v>
       </c>
       <c r="D116" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="117">
@@ -6510,7 +6510,7 @@
         <v>6</v>
       </c>
       <c r="D117" s="25" t="n">
-        <v>0.1132075471698113</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="118">
@@ -6523,7 +6523,7 @@
         <v>7</v>
       </c>
       <c r="D118" s="25" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="119">
@@ -6536,7 +6536,7 @@
         <v>21</v>
       </c>
       <c r="D119" s="25" t="n">
-        <v>0.3962264150943396</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="120">
@@ -6549,7 +6549,7 @@
         <v>5</v>
       </c>
       <c r="D120" s="25" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="121">
@@ -6562,7 +6562,7 @@
         <v>2</v>
       </c>
       <c r="D121" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="122">
@@ -6575,7 +6575,7 @@
         <v>2</v>
       </c>
       <c r="D122" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="123">
@@ -6588,7 +6588,7 @@
         <v>6</v>
       </c>
       <c r="D123" s="25" t="n">
-        <v>0.1132075471698113</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="124">
@@ -6601,7 +6601,7 @@
         <v>34</v>
       </c>
       <c r="D124" s="25" t="n">
-        <v>0.6415094339622641</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="125">
@@ -6652,7 +6652,7 @@
         <v>20</v>
       </c>
       <c r="D128" s="25" t="n">
-        <v>0.3773584905660378</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="129">
@@ -6665,7 +6665,7 @@
         <v>29</v>
       </c>
       <c r="D129" s="25" t="n">
-        <v>0.5471698113207547</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="130">
@@ -6678,7 +6678,7 @@
         <v>29</v>
       </c>
       <c r="D130" s="25" t="n">
-        <v>0.5471698113207547</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="131">
@@ -6704,7 +6704,7 @@
         <v>10</v>
       </c>
       <c r="D132" s="25" t="n">
-        <v>0.1886792452830189</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="133">
@@ -6717,7 +6717,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="134">
@@ -6730,7 +6730,7 @@
         <v>2</v>
       </c>
       <c r="D134" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="135">
@@ -6781,7 +6781,7 @@
         <v>24</v>
       </c>
       <c r="D138" s="25" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="139">
@@ -6794,7 +6794,7 @@
         <v>20</v>
       </c>
       <c r="D139" s="25" t="n">
-        <v>0.3773584905660378</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="140">
@@ -6807,7 +6807,7 @@
         <v>24</v>
       </c>
       <c r="D140" s="25" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="141">
@@ -6820,7 +6820,7 @@
         <v>12</v>
       </c>
       <c r="D141" s="25" t="n">
-        <v>0.2264150943396226</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="142">
@@ -6833,7 +6833,7 @@
         <v>9</v>
       </c>
       <c r="D142" s="25" t="n">
-        <v>0.169811320754717</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="143">
@@ -6846,7 +6846,7 @@
         <v>13</v>
       </c>
       <c r="D143" s="25" t="n">
-        <v>0.2452830188679245</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="144">
@@ -6859,7 +6859,7 @@
         <v>16</v>
       </c>
       <c r="D144" s="25" t="n">
-        <v>0.3018867924528302</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="145">
@@ -6910,7 +6910,7 @@
         <v>33</v>
       </c>
       <c r="D148" s="25" t="n">
-        <v>0.6226415094339622</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="149">
@@ -6923,7 +6923,7 @@
         <v>15</v>
       </c>
       <c r="D149" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="150">
@@ -6936,7 +6936,7 @@
         <v>2</v>
       </c>
       <c r="D150" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="151">
@@ -7026,7 +7026,7 @@
         <v>1</v>
       </c>
       <c r="D157" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="158">
@@ -7039,7 +7039,7 @@
         <v>49</v>
       </c>
       <c r="D158" s="25" t="n">
-        <v>0.9245283018867925</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="159">
@@ -7090,7 +7090,7 @@
         <v>1</v>
       </c>
       <c r="D162" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="163">
@@ -7103,7 +7103,7 @@
         <v>1</v>
       </c>
       <c r="D163" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="164">
@@ -7154,7 +7154,7 @@
         <v>1</v>
       </c>
       <c r="D167" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="168">
@@ -7167,7 +7167,7 @@
         <v>5</v>
       </c>
       <c r="D168" s="25" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="169">
@@ -7193,7 +7193,7 @@
         <v>2</v>
       </c>
       <c r="D170" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="171">
@@ -7219,7 +7219,7 @@
         <v>40</v>
       </c>
       <c r="D172" s="25" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="173">
@@ -7232,7 +7232,7 @@
         <v>2</v>
       </c>
       <c r="D173" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="174">
@@ -7283,7 +7283,7 @@
         <v>1</v>
       </c>
       <c r="D177" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="178">
@@ -7296,7 +7296,7 @@
         <v>30</v>
       </c>
       <c r="D178" s="25" t="n">
-        <v>0.5660377358490566</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="179">
@@ -7309,7 +7309,7 @@
         <v>24</v>
       </c>
       <c r="D179" s="25" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="180">
@@ -7322,7 +7322,7 @@
         <v>28</v>
       </c>
       <c r="D180" s="25" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -7335,7 +7335,7 @@
         <v>15</v>
       </c>
       <c r="D181" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="182">
@@ -7348,7 +7348,7 @@
         <v>10</v>
       </c>
       <c r="D182" s="25" t="n">
-        <v>0.1886792452830189</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="183">
@@ -7361,7 +7361,7 @@
         <v>24</v>
       </c>
       <c r="D183" s="25" t="n">
-        <v>0.4528301886792453</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="184">
@@ -7374,7 +7374,7 @@
         <v>7</v>
       </c>
       <c r="D184" s="25" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="185">
@@ -7387,7 +7387,7 @@
         <v>4</v>
       </c>
       <c r="D185" s="25" t="n">
-        <v>0.07547169811320754</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="186">
@@ -7400,7 +7400,7 @@
         <v>4</v>
       </c>
       <c r="D186" s="25" t="n">
-        <v>0.07547169811320754</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="187">
@@ -7451,7 +7451,7 @@
         <v>36</v>
       </c>
       <c r="D190" s="25" t="n">
-        <v>0.6792452830188679</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="191">
@@ -7464,7 +7464,7 @@
         <v>15</v>
       </c>
       <c r="D191" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="192">
@@ -7477,7 +7477,7 @@
         <v>14</v>
       </c>
       <c r="D192" s="25" t="n">
-        <v>0.2641509433962264</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="193">
@@ -7490,7 +7490,7 @@
         <v>15</v>
       </c>
       <c r="D193" s="25" t="n">
-        <v>0.2830188679245283</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="194">
@@ -7503,7 +7503,7 @@
         <v>3</v>
       </c>
       <c r="D194" s="25" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="195">
@@ -7516,7 +7516,7 @@
         <v>5</v>
       </c>
       <c r="D195" s="25" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="196">
@@ -7529,7 +7529,7 @@
         <v>8</v>
       </c>
       <c r="D196" s="25" t="n">
-        <v>0.1509433962264151</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="197">
@@ -7542,7 +7542,7 @@
         <v>7</v>
       </c>
       <c r="D197" s="25" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="198">
@@ -7593,7 +7593,7 @@
         <v>29</v>
       </c>
       <c r="D201" s="25" t="n">
-        <v>0.5471698113207547</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="202">
@@ -7606,7 +7606,7 @@
         <v>11</v>
       </c>
       <c r="D202" s="25" t="n">
-        <v>0.2075471698113208</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="203">
@@ -7619,7 +7619,7 @@
         <v>10</v>
       </c>
       <c r="D203" s="25" t="n">
-        <v>0.1886792452830189</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="204">
@@ -7670,7 +7670,7 @@
         <v>29</v>
       </c>
       <c r="D207" s="25" t="n">
-        <v>0.5471698113207547</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="208">
@@ -7683,7 +7683,7 @@
         <v>21</v>
       </c>
       <c r="D208" s="25" t="n">
-        <v>0.3962264150943396</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="209">
@@ -7734,7 +7734,7 @@
         <v>6</v>
       </c>
       <c r="D212" s="25" t="n">
-        <v>0.1132075471698113</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="213">
@@ -7747,7 +7747,7 @@
         <v>11</v>
       </c>
       <c r="D213" s="25" t="n">
-        <v>0.2075471698113208</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="214">
@@ -7760,7 +7760,7 @@
         <v>9</v>
       </c>
       <c r="D214" s="25" t="n">
-        <v>0.169811320754717</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="215">
@@ -7773,7 +7773,7 @@
         <v>3</v>
       </c>
       <c r="D215" s="25" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="216">
@@ -7837,7 +7837,7 @@
         <v>12</v>
       </c>
       <c r="D220" s="25" t="n">
-        <v>0.2264150943396226</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="221">
@@ -7863,7 +7863,7 @@
         <v>2</v>
       </c>
       <c r="D222" s="25" t="n">
-        <v>0.03773584905660377</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="223">
@@ -7876,7 +7876,7 @@
         <v>4</v>
       </c>
       <c r="D223" s="25" t="n">
-        <v>0.07547169811320754</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="224">
@@ -7889,7 +7889,7 @@
         <v>3</v>
       </c>
       <c r="D224" s="25" t="n">
-        <v>0.05660377358490566</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="225">
@@ -7902,7 +7902,7 @@
         <v>20</v>
       </c>
       <c r="D225" s="25" t="n">
-        <v>0.3773584905660378</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="226">
@@ -7915,7 +7915,7 @@
         <v>9</v>
       </c>
       <c r="D226" s="25" t="n">
-        <v>0.169811320754717</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="227">
@@ -7966,7 +7966,7 @@
         <v>13</v>
       </c>
       <c r="D230" s="25" t="n">
-        <v>0.2452830188679245</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="231">
@@ -7979,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="D231" s="25" t="n">
-        <v>0.01886792452830189</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="232">
@@ -8031,7 +8031,7 @@
         <v>39</v>
       </c>
       <c r="D235" s="25" t="n">
-        <v>0.7358490566037735</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="236">
@@ -8082,7 +8082,7 @@
         <v>7</v>
       </c>
       <c r="D239" s="25" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="240">
@@ -8095,7 +8095,7 @@
         <v>8</v>
       </c>
       <c r="D240" s="25" t="n">
-        <v>0.1509433962264151</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="241">
@@ -8108,7 +8108,7 @@
         <v>4</v>
       </c>
       <c r="D241" s="25" t="n">
-        <v>0.07547169811320754</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="242">
@@ -8121,7 +8121,7 @@
         <v>5</v>
       </c>
       <c r="D242" s="25" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="243">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C248" s="32" t="inlineStr">
         <is>
-          <t>3.0 Years</t>
+          <t>2.9 Years</t>
         </is>
       </c>
     </row>

--- a/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Dausa/excel/Dausa_Survey_Analysis_Master.xlsx
+++ b/Projects/CmF_SHG_Women_Entrepreneurs/reports/district_analysis/Dausa/excel/Dausa_Survey_Analysis_Master.xlsx
@@ -816,22 +816,22 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>2253000</v>
+        <v>1621000</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>281625</v>
+        <v>231571.4285714286</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>175000</v>
+        <v>150000</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1139000</v>
+        <v>729000</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>0</v>
@@ -840,16 +840,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="7" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="M4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>309000</v>
+        <v>252000</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>320000</v>
+        <v>280000</v>
       </c>
       <c r="P4" s="7" t="n">
         <v>80000</v>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -945,23 +945,23 @@
           <t>Apparel/fabric</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>73000</v>
+      <c r="D6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>73000</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>12000</v>
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="7" t="n">
-        <v>31000</v>
+      <c r="I6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>0</v>
@@ -978,8 +978,8 @@
       <c r="N6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="7" t="n">
-        <v>30000</v>
+      <c r="O6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="P6" s="8" t="n">
         <v>0</v>
@@ -996,8 +996,8 @@
       <c r="T6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="6" t="n">
-        <v>1</v>
+      <c r="U6" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
@@ -3895,7 +3895,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3940,14 +3940,14 @@
       <c r="E7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>1</v>
+      <c r="F7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="6" t="n">
-        <v>1</v>
+      <c r="H7" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
